--- a/regression_deneme/regression_with_nn/anadolu caddesi_monthly_true_and_predicted_test.xlsx
+++ b/regression_deneme/regression_with_nn/anadolu caddesi_monthly_true_and_predicted_test.xlsx
@@ -461,7 +461,7 @@
         <v>58</v>
       </c>
       <c r="D2" t="n">
-        <v>57.39135778971674</v>
+        <v>52.01290109907212</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>48</v>
       </c>
       <c r="D3" t="n">
-        <v>56.48613589599351</v>
+        <v>59.6842759999071</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>58</v>
       </c>
       <c r="D4" t="n">
-        <v>53.68351558237069</v>
+        <v>57.76022864574952</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>58.69196654100326</v>
+        <v>63.99521230552731</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>43.64343115416364</v>
+        <v>47.6675517427007</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>50.53273684191771</v>
+        <v>58.67439737937556</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>52.35571688157142</v>
+        <v>52.50476565639187</v>
       </c>
     </row>
   </sheetData>
